--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 07/XKSX_NapChanVoHopVNSH03_03072026.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 07/XKSX_NapChanVoHopVNSH03_03072026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B957B486-034A-4D78-87EA-78A03AD26E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABA4976-D005-4A66-B39E-BCE1EBE8D188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -488,6 +488,63 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -499,63 +556,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -981,66 +981,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="40" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="42"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="44"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="43" t="s">
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="44"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="40"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="37"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="45" t="s">
+      <c r="A4" s="33"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="46"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="42"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="30"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="23"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E11" s="21"/>
       <c r="F11" s="17"/>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="43" t="s">
         <v>30</v>
       </c>
       <c r="H11" s="21" t="s">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E12" s="21"/>
       <c r="F12" s="17"/>
-      <c r="G12" s="25"/>
+      <c r="G12" s="44"/>
       <c r="H12" s="21" t="s">
         <v>26</v>
       </c>
@@ -1177,40 +1177,40 @@
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27" t="s">
+      <c r="B15" s="46"/>
+      <c r="C15" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27" t="s">
+      <c r="D15" s="46"/>
+      <c r="E15" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27" t="s">
+      <c r="F15" s="46"/>
+      <c r="G15" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="H15" s="27"/>
+      <c r="H15" s="46"/>
     </row>
     <row r="16" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26" t="s">
+      <c r="B16" s="45"/>
+      <c r="C16" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26" t="s">
+      <c r="D16" s="45"/>
+      <c r="E16" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26" t="s">
+      <c r="F16" s="45"/>
+      <c r="G16" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="26"/>
+      <c r="H16" s="45"/>
     </row>
     <row r="17" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13"/>
@@ -1263,22 +1263,22 @@
       <c r="H21" s="13"/>
     </row>
     <row r="22" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27" t="s">
+      <c r="B22" s="46"/>
+      <c r="C22" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27" t="s">
+      <c r="D22" s="46"/>
+      <c r="E22" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27" t="s">
+      <c r="F22" s="46"/>
+      <c r="G22" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="H22" s="27"/>
+      <c r="H22" s="46"/>
     </row>
     <row r="23" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1304,12 +1304,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A15:B15"/>
@@ -1323,6 +1317,12 @@
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G22:H22"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="2" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
